--- a/SITUATION DE PRODUCTION 2025-2026.xlsx
+++ b/SITUATION DE PRODUCTION 2025-2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10322"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7073E96-2B24-AA4A-9350-6371AD1EE4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC98EBCD-5038-D34A-8A85-9BDC4544462E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="860" yWindow="760" windowWidth="25720" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SITUATION LOCAL 2025-2026 " sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7542" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7682" uniqueCount="108">
   <si>
     <t>Comptabilité</t>
   </si>
@@ -364,6 +364,15 @@
   </si>
   <si>
     <t>SEMAINE 13</t>
+  </si>
+  <si>
+    <t>CASCADE MYRTILLE S8</t>
+  </si>
+  <si>
+    <t>AAAA</t>
+  </si>
+  <si>
+    <t>BBBB</t>
   </si>
 </sst>
 </file>
@@ -1558,49 +1567,6 @@
     <xf numFmtId="166" fontId="9" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1654,6 +1620,49 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1984,20 +1993,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="I2" s="125">
+      <c r="I2" s="108">
         <f>SUM(I5:I889)</f>
         <v>27846.369999999995</v>
       </c>
-      <c r="J2" s="127"/>
-      <c r="K2" s="125">
+      <c r="J2" s="110"/>
+      <c r="K2" s="108">
         <f>SUM(K5:K485)</f>
         <v>177677.23000000004</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="I3" s="126"/>
-      <c r="J3" s="128"/>
-      <c r="K3" s="126"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="109"/>
     </row>
     <row r="4" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -19533,7 +19542,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A494" s="6" t="s">
         <v>91</v>
       </c>
@@ -19603,7 +19612,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="496" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A496" s="6" t="s">
         <v>91</v>
       </c>
@@ -19708,7 +19717,7 @@
         <v>229.59999999999997</v>
       </c>
     </row>
-    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A499" s="6" t="s">
         <v>92</v>
       </c>
@@ -21807,7 +21816,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" s="6" t="s">
         <v>96</v>
       </c>
@@ -22122,7 +22131,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="568" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A568" s="6" t="s">
         <v>98</v>
       </c>
@@ -22783,7 +22792,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="587" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A587" s="6" t="s">
         <v>99</v>
       </c>
@@ -23588,7 +23597,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="610" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A610" s="6" t="s">
         <v>99</v>
       </c>
@@ -23693,7 +23702,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="613" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A613" s="6" t="s">
         <v>99</v>
       </c>
@@ -23834,7 +23843,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" s="6" t="s">
         <v>99</v>
       </c>
@@ -24849,7 +24858,7 @@
         <v>3525</v>
       </c>
     </row>
-    <row r="646" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A646" s="6" t="s">
         <v>104</v>
       </c>
@@ -24951,7 +24960,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="649" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A649" s="6" t="s">
         <v>104</v>
       </c>
@@ -24995,11 +25004,9 @@
         <dateGroupItem year="2026" dateTimeGrouping="year"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="9">
+    <filterColumn colId="7">
       <filters>
-        <filter val="65.00 DH"/>
-        <filter val="70.00 DH"/>
-        <filter val="75.00 DH"/>
+        <filter val="CORINA MYRTILLE S8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -25057,7 +25064,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:AB1408"/>
+  <dimension ref="A2:AB1410"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -25074,15 +25081,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="I2" s="129">
-        <f>SUM(I5:I1895)</f>
-        <v>93739.9</v>
-      </c>
-      <c r="J2" s="131"/>
-      <c r="K2" s="131"/>
+      <c r="I2" s="112">
+        <f>SUM(I5:I1897)</f>
+        <v>101755.9</v>
+      </c>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
     </row>
     <row r="3" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="I3" s="130"/>
+      <c r="I3" s="113"/>
     </row>
     <row r="4" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -44703,303 +44710,809 @@
       </c>
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A554" s="6"/>
-      <c r="B554" s="6"/>
-      <c r="C554" s="6"/>
-      <c r="D554" s="6"/>
-      <c r="E554" s="6"/>
-      <c r="F554" s="7"/>
-      <c r="G554" s="8"/>
-      <c r="H554" s="6"/>
-      <c r="I554" s="9"/>
-      <c r="J554" s="10"/>
-      <c r="K554" s="10"/>
+      <c r="A554" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B554" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C554" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D554" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E554" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F554" s="98">
+        <v>46106</v>
+      </c>
+      <c r="G554" s="8">
+        <v>7506</v>
+      </c>
+      <c r="H554" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I554" s="9">
+        <v>379.5</v>
+      </c>
+      <c r="J554" s="10">
+        <v>0</v>
+      </c>
+      <c r="K554" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="555" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A555" s="6"/>
-      <c r="B555" s="6"/>
-      <c r="C555" s="6"/>
-      <c r="D555" s="6"/>
-      <c r="E555" s="6"/>
-      <c r="F555" s="7"/>
-      <c r="G555" s="8"/>
-      <c r="H555" s="6"/>
-      <c r="I555" s="9"/>
-      <c r="J555" s="10"/>
-      <c r="K555" s="10"/>
+      <c r="A555" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B555" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C555" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D555" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E555" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F555" s="98">
+        <v>46106</v>
+      </c>
+      <c r="G555" s="8">
+        <v>7505</v>
+      </c>
+      <c r="H555" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I555" s="9">
+        <v>873</v>
+      </c>
+      <c r="J555" s="10">
+        <v>0</v>
+      </c>
+      <c r="K555" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="556" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A556" s="6"/>
-      <c r="B556" s="6"/>
-      <c r="C556" s="6"/>
-      <c r="D556" s="6"/>
-      <c r="E556" s="6"/>
-      <c r="F556" s="7"/>
-      <c r="G556" s="8"/>
-      <c r="H556" s="6"/>
-      <c r="I556" s="9"/>
-      <c r="J556" s="10"/>
-      <c r="K556" s="10"/>
+      <c r="A556" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B556" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C556" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D556" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E556" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F556" s="98">
+        <v>46106</v>
+      </c>
+      <c r="G556">
+        <v>6681</v>
+      </c>
+      <c r="H556" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I556" s="9">
+        <v>685.5</v>
+      </c>
+      <c r="J556" s="10">
+        <v>0</v>
+      </c>
+      <c r="K556" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A557" s="6"/>
-      <c r="B557" s="6"/>
-      <c r="C557" s="6"/>
-      <c r="D557" s="6"/>
-      <c r="E557" s="6"/>
-      <c r="F557" s="7"/>
-      <c r="G557" s="8"/>
-      <c r="H557" s="6"/>
-      <c r="I557" s="9"/>
-      <c r="J557" s="10"/>
-      <c r="K557" s="10"/>
+      <c r="A557" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B557" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C557" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D557" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E557" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F557" s="98">
+        <v>45742</v>
+      </c>
+      <c r="G557" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H557" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I557" s="9">
+        <v>355.5</v>
+      </c>
+      <c r="J557" s="10">
+        <v>0</v>
+      </c>
+      <c r="K557" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="558" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A558" s="6"/>
-      <c r="B558" s="6"/>
-      <c r="C558" s="6"/>
-      <c r="D558" s="6"/>
-      <c r="E558" s="6"/>
-      <c r="F558" s="7"/>
-      <c r="G558" s="8"/>
-      <c r="H558" s="6"/>
-      <c r="I558" s="9"/>
-      <c r="J558" s="10"/>
-      <c r="K558" s="10"/>
+      <c r="A558" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B558" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C558" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D558" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E558" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F558" s="98">
+        <v>45742</v>
+      </c>
+      <c r="G558" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H558" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I558" s="9">
+        <v>334.5</v>
+      </c>
+      <c r="J558" s="10">
+        <v>0</v>
+      </c>
+      <c r="K558" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A559" s="6"/>
-      <c r="B559" s="6"/>
-      <c r="C559" s="6"/>
-      <c r="D559" s="6"/>
-      <c r="E559" s="6"/>
-      <c r="F559" s="7"/>
-      <c r="G559" s="8"/>
-      <c r="H559" s="6"/>
-      <c r="I559" s="9"/>
-      <c r="J559" s="10"/>
-      <c r="K559" s="10"/>
+      <c r="A559" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B559" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C559" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D559" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E559" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F559" s="98">
+        <v>45742</v>
+      </c>
+      <c r="G559" s="8">
+        <v>7507</v>
+      </c>
+      <c r="H559" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I559" s="9">
+        <v>706.5</v>
+      </c>
+      <c r="J559" s="10">
+        <v>0</v>
+      </c>
+      <c r="K559" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="560" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A560" s="6"/>
-      <c r="B560" s="6"/>
-      <c r="C560" s="6"/>
-      <c r="D560" s="6"/>
-      <c r="E560" s="6"/>
-      <c r="F560" s="7"/>
-      <c r="G560" s="8"/>
-      <c r="H560" s="6"/>
-      <c r="I560" s="9"/>
-      <c r="J560" s="10"/>
-      <c r="K560" s="10"/>
+      <c r="A560" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B560" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C560" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D560" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E560" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F560" s="98">
+        <v>45742</v>
+      </c>
+      <c r="G560" s="8">
+        <v>7508</v>
+      </c>
+      <c r="H560" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I560" s="9">
+        <v>388.5</v>
+      </c>
+      <c r="J560" s="10">
+        <v>0</v>
+      </c>
+      <c r="K560" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="561" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A561" s="6"/>
-      <c r="B561" s="6"/>
-      <c r="C561" s="6"/>
-      <c r="D561" s="6"/>
-      <c r="E561" s="6"/>
-      <c r="F561" s="7"/>
-      <c r="G561" s="8"/>
-      <c r="H561" s="6"/>
-      <c r="I561" s="9"/>
-      <c r="J561" s="10"/>
-      <c r="K561" s="10"/>
+      <c r="A561" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B561" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C561" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D561" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E561" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F561" s="98">
+        <v>45743</v>
+      </c>
+      <c r="G561" s="8">
+        <v>6686</v>
+      </c>
+      <c r="H561" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="I561" s="9">
+        <v>180</v>
+      </c>
+      <c r="J561" s="10">
+        <v>0</v>
+      </c>
+      <c r="K561" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="562" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A562" s="6"/>
-      <c r="B562" s="6"/>
-      <c r="C562" s="6"/>
-      <c r="D562" s="6"/>
-      <c r="E562" s="6"/>
-      <c r="F562" s="7"/>
-      <c r="G562" s="8"/>
-      <c r="H562" s="6"/>
-      <c r="I562" s="9"/>
-      <c r="J562" s="10"/>
-      <c r="K562" s="10"/>
+      <c r="A562" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B562" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C562" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D562" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E562" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F562" s="98">
+        <v>45743</v>
+      </c>
+      <c r="G562" s="8">
+        <v>6688</v>
+      </c>
+      <c r="H562" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="I562" s="9">
+        <v>204</v>
+      </c>
+      <c r="J562" s="10">
+        <v>0</v>
+      </c>
+      <c r="K562" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="563" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A563" s="6"/>
-      <c r="B563" s="6"/>
-      <c r="C563" s="6"/>
-      <c r="D563" s="6"/>
-      <c r="E563" s="6"/>
-      <c r="F563" s="7"/>
-      <c r="G563" s="8"/>
-      <c r="H563" s="6"/>
-      <c r="I563" s="9"/>
-      <c r="J563" s="10"/>
-      <c r="K563" s="10"/>
+      <c r="A563" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B563" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C563" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D563" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E563" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F563" s="98">
+        <v>45743</v>
+      </c>
+      <c r="G563" s="8">
+        <v>7509</v>
+      </c>
+      <c r="H563" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I563" s="9">
+        <v>781.5</v>
+      </c>
+      <c r="J563" s="10">
+        <v>0</v>
+      </c>
+      <c r="K563" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="564" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A564" s="6"/>
-      <c r="B564" s="6"/>
-      <c r="C564" s="6"/>
-      <c r="D564" s="6"/>
-      <c r="E564" s="6"/>
-      <c r="F564" s="7"/>
-      <c r="G564" s="8"/>
-      <c r="H564" s="6"/>
-      <c r="I564" s="9"/>
-      <c r="J564" s="10"/>
-      <c r="K564" s="10"/>
+      <c r="A564" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B564" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C564" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D564" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E564" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F564" s="98">
+        <v>45743</v>
+      </c>
+      <c r="G564" s="8">
+        <v>7510</v>
+      </c>
+      <c r="H564" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I564" s="9">
+        <v>483</v>
+      </c>
+      <c r="J564" s="10">
+        <v>0</v>
+      </c>
+      <c r="K564" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="565" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A565" s="6"/>
-      <c r="B565" s="6"/>
-      <c r="C565" s="6"/>
-      <c r="D565" s="6"/>
-      <c r="E565" s="6"/>
-      <c r="F565" s="7"/>
-      <c r="G565" s="8"/>
-      <c r="H565" s="6"/>
-      <c r="I565" s="9"/>
-      <c r="J565" s="10"/>
-      <c r="K565" s="10"/>
+      <c r="A565" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B565" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C565" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D565" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E565" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F565" s="98">
+        <v>45744</v>
+      </c>
+      <c r="G565" s="8">
+        <v>7511</v>
+      </c>
+      <c r="H565" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I565" s="9">
+        <v>307.5</v>
+      </c>
+      <c r="J565" s="10">
+        <v>0</v>
+      </c>
+      <c r="K565" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="566" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A566" s="6"/>
-      <c r="B566" s="6"/>
-      <c r="C566" s="6"/>
-      <c r="D566" s="6"/>
-      <c r="E566" s="6"/>
-      <c r="F566" s="7"/>
-      <c r="G566" s="8"/>
-      <c r="H566" s="6"/>
-      <c r="I566" s="9"/>
-      <c r="J566" s="10"/>
-      <c r="K566" s="10"/>
+      <c r="A566" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B566" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C566" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D566" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E566" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F566" s="98">
+        <v>45744</v>
+      </c>
+      <c r="G566" s="8">
+        <v>7512</v>
+      </c>
+      <c r="H566" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I566" s="9">
+        <v>501</v>
+      </c>
+      <c r="J566" s="10">
+        <v>0</v>
+      </c>
+      <c r="K566" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A567" s="6"/>
-      <c r="B567" s="6"/>
-      <c r="C567" s="6"/>
-      <c r="D567" s="6"/>
-      <c r="E567" s="6"/>
-      <c r="F567" s="7"/>
-      <c r="G567" s="8"/>
-      <c r="H567" s="6"/>
-      <c r="I567" s="9"/>
-      <c r="J567" s="10"/>
-      <c r="K567" s="10"/>
+      <c r="A567" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B567" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C567" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D567" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E567" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F567" s="98">
+        <v>45744</v>
+      </c>
+      <c r="G567" s="8">
+        <v>7513</v>
+      </c>
+      <c r="H567" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I567" s="9">
+        <v>291</v>
+      </c>
+      <c r="J567" s="10">
+        <v>0</v>
+      </c>
+      <c r="K567" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="568" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A568" s="6"/>
-      <c r="B568" s="6"/>
-      <c r="C568" s="6"/>
-      <c r="D568" s="6"/>
-      <c r="E568" s="6"/>
-      <c r="F568" s="7"/>
-      <c r="G568" s="8"/>
-      <c r="H568" s="6"/>
-      <c r="I568" s="9"/>
-      <c r="J568" s="10"/>
-      <c r="K568" s="10"/>
+      <c r="A568" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B568" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C568" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D568" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E568" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F568" s="98">
+        <v>46109</v>
+      </c>
+      <c r="G568" s="8">
+        <v>6693</v>
+      </c>
+      <c r="H568" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I568" s="9">
+        <v>34.5</v>
+      </c>
+      <c r="J568" s="10">
+        <v>0</v>
+      </c>
+      <c r="K568" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="569" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A569" s="6"/>
-      <c r="B569" s="6"/>
-      <c r="C569" s="6"/>
-      <c r="D569" s="6"/>
-      <c r="E569" s="6"/>
-      <c r="F569" s="7"/>
-      <c r="G569" s="8"/>
-      <c r="H569" s="6"/>
-      <c r="I569" s="9"/>
-      <c r="J569" s="10"/>
-      <c r="K569" s="10"/>
+      <c r="A569" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B569" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C569" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D569" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E569" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F569" s="98">
+        <v>46109</v>
+      </c>
+      <c r="G569" s="8">
+        <v>6689</v>
+      </c>
+      <c r="H569" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I569" s="9">
+        <v>180</v>
+      </c>
+      <c r="J569" s="10">
+        <v>0</v>
+      </c>
+      <c r="K569" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A570" s="6"/>
-      <c r="B570" s="6"/>
-      <c r="C570" s="6"/>
-      <c r="D570" s="6"/>
-      <c r="E570" s="6"/>
-      <c r="F570" s="7"/>
-      <c r="G570" s="8"/>
-      <c r="H570" s="6"/>
-      <c r="I570" s="9"/>
-      <c r="J570" s="10"/>
-      <c r="K570" s="10"/>
+      <c r="A570" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B570" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C570" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D570" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E570" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F570" s="98">
+        <v>46109</v>
+      </c>
+      <c r="G570" s="8">
+        <v>6692</v>
+      </c>
+      <c r="H570" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I570" s="9">
+        <v>145.5</v>
+      </c>
+      <c r="J570" s="10">
+        <v>0</v>
+      </c>
+      <c r="K570" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="571" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A571" s="6"/>
-      <c r="B571" s="6"/>
-      <c r="C571" s="6"/>
-      <c r="D571" s="6"/>
-      <c r="E571" s="6"/>
-      <c r="F571" s="7"/>
-      <c r="G571" s="8"/>
-      <c r="H571" s="6"/>
-      <c r="I571" s="9"/>
-      <c r="J571" s="10"/>
-      <c r="K571" s="10"/>
+      <c r="A571" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B571" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C571" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D571" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E571" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F571" s="98">
+        <v>46110</v>
+      </c>
+      <c r="G571" s="8">
+        <v>7514</v>
+      </c>
+      <c r="H571" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I571" s="9">
+        <v>187.5</v>
+      </c>
+      <c r="J571" s="10">
+        <v>0</v>
+      </c>
+      <c r="K571" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="572" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A572" s="6"/>
-      <c r="B572" s="6"/>
-      <c r="C572" s="6"/>
-      <c r="D572" s="6"/>
-      <c r="E572" s="6"/>
-      <c r="F572" s="7"/>
-      <c r="G572" s="8"/>
-      <c r="H572" s="6"/>
-      <c r="I572" s="9"/>
-      <c r="J572" s="10"/>
-      <c r="K572" s="10"/>
+      <c r="A572" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B572" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C572" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D572" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E572" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F572" s="98">
+        <v>46110</v>
+      </c>
+      <c r="G572" s="8">
+        <v>7515</v>
+      </c>
+      <c r="H572" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I572" s="9">
+        <v>532.79999999999995</v>
+      </c>
+      <c r="J572" s="10">
+        <v>0</v>
+      </c>
+      <c r="K572" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="573" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A573" s="6"/>
-      <c r="B573" s="6"/>
-      <c r="C573" s="6"/>
-      <c r="D573" s="6"/>
-      <c r="E573" s="6"/>
-      <c r="F573" s="7"/>
-      <c r="G573" s="8"/>
-      <c r="H573" s="6"/>
-      <c r="I573" s="9"/>
-      <c r="J573" s="10"/>
-      <c r="K573" s="10"/>
+      <c r="A573" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B573" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C573" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D573" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E573" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F573" s="98">
+        <v>46110</v>
+      </c>
+      <c r="G573" s="8">
+        <v>6695</v>
+      </c>
+      <c r="H573" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I573" s="9">
+        <v>187.2</v>
+      </c>
+      <c r="J573" s="10">
+        <v>0</v>
+      </c>
+      <c r="K573" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="574" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A574" s="6"/>
-      <c r="B574" s="6"/>
-      <c r="C574" s="6"/>
-      <c r="D574" s="6"/>
-      <c r="E574" s="6"/>
-      <c r="F574" s="7"/>
-      <c r="G574" s="8"/>
-      <c r="H574" s="6"/>
-      <c r="I574" s="9"/>
-      <c r="J574" s="10"/>
-      <c r="K574" s="10"/>
+      <c r="A574" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B574" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C574" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D574" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E574" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F574" s="98">
+        <v>46110</v>
+      </c>
+      <c r="G574" s="8">
+        <v>6696</v>
+      </c>
+      <c r="H574" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I574" s="9">
+        <v>43.5</v>
+      </c>
+      <c r="J574" s="10">
+        <v>0</v>
+      </c>
+      <c r="K574" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="575" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A575" s="6"/>
-      <c r="B575" s="6"/>
-      <c r="C575" s="6"/>
-      <c r="D575" s="6"/>
-      <c r="E575" s="6"/>
-      <c r="F575" s="7"/>
-      <c r="G575" s="8"/>
-      <c r="H575" s="6"/>
-      <c r="I575" s="9"/>
-      <c r="J575" s="10"/>
-      <c r="K575" s="10"/>
+      <c r="A575" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B575" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C575" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D575" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E575" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F575" s="98">
+        <v>46110</v>
+      </c>
+      <c r="G575" s="8">
+        <v>7514</v>
+      </c>
+      <c r="H575" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I575" s="9">
+        <v>223.5</v>
+      </c>
+      <c r="J575" s="10">
+        <v>0</v>
+      </c>
+      <c r="K575" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="576" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A576" s="6"/>
-      <c r="B576" s="6"/>
-      <c r="C576" s="6"/>
-      <c r="D576" s="6"/>
-      <c r="E576" s="6"/>
-      <c r="F576" s="7"/>
-      <c r="G576" s="8"/>
-      <c r="H576" s="6"/>
-      <c r="I576" s="9"/>
-      <c r="J576" s="10"/>
-      <c r="K576" s="10"/>
+      <c r="A576" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B576" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C576" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D576" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E576" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F576" s="98">
+        <v>46110</v>
+      </c>
+      <c r="G576" s="8">
+        <v>6693</v>
+      </c>
+      <c r="H576" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I576" s="9">
+        <v>10.5</v>
+      </c>
+      <c r="J576" s="10">
+        <v>0</v>
+      </c>
+      <c r="K576" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="577" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A577" s="6"/>
@@ -45495,7 +46008,7 @@
       <c r="J614" s="10"/>
       <c r="K614" s="10"/>
     </row>
-    <row r="615" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A615" s="6"/>
       <c r="B615" s="6"/>
       <c r="C615" s="6"/>
@@ -45507,21 +46020,6 @@
       <c r="I615" s="9"/>
       <c r="J615" s="10"/>
       <c r="K615" s="10"/>
-      <c r="L615" s="6"/>
-      <c r="M615" s="6"/>
-      <c r="N615" s="6"/>
-      <c r="O615" s="6"/>
-      <c r="P615" s="6"/>
-      <c r="Q615" s="6"/>
-      <c r="R615" s="6"/>
-      <c r="S615" s="6"/>
-      <c r="T615" s="6"/>
-      <c r="U615" s="6"/>
-      <c r="V615" s="6"/>
-      <c r="W615" s="6"/>
-      <c r="X615" s="6"/>
-      <c r="Y615" s="6"/>
-      <c r="Z615" s="6"/>
     </row>
     <row r="616" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A616" s="6"/>
@@ -45564,7 +46062,7 @@
       <c r="Y617" s="6"/>
       <c r="Z617" s="6"/>
     </row>
-    <row r="618" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A618" s="6"/>
       <c r="B618" s="6"/>
       <c r="C618" s="6"/>
@@ -45576,21 +46074,6 @@
       <c r="I618" s="9"/>
       <c r="J618" s="10"/>
       <c r="K618" s="10"/>
-      <c r="L618" s="6"/>
-      <c r="M618" s="6"/>
-      <c r="N618" s="6"/>
-      <c r="O618" s="6"/>
-      <c r="P618" s="6"/>
-      <c r="Q618" s="6"/>
-      <c r="R618" s="6"/>
-      <c r="S618" s="6"/>
-      <c r="T618" s="6"/>
-      <c r="U618" s="6"/>
-      <c r="V618" s="6"/>
-      <c r="W618" s="6"/>
-      <c r="X618" s="6"/>
-      <c r="Y618" s="6"/>
-      <c r="Z618" s="6"/>
     </row>
     <row r="619" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="6"/>
@@ -45704,7 +46187,7 @@
       <c r="Y622" s="6"/>
       <c r="Z622" s="6"/>
     </row>
-    <row r="623" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="6"/>
       <c r="B623" s="6"/>
       <c r="C623" s="6"/>
@@ -45716,8 +46199,23 @@
       <c r="I623" s="9"/>
       <c r="J623" s="10"/>
       <c r="K623" s="10"/>
-    </row>
-    <row r="624" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="L623" s="6"/>
+      <c r="M623" s="6"/>
+      <c r="N623" s="6"/>
+      <c r="O623" s="6"/>
+      <c r="P623" s="6"/>
+      <c r="Q623" s="6"/>
+      <c r="R623" s="6"/>
+      <c r="S623" s="6"/>
+      <c r="T623" s="6"/>
+      <c r="U623" s="6"/>
+      <c r="V623" s="6"/>
+      <c r="W623" s="6"/>
+      <c r="X623" s="6"/>
+      <c r="Y623" s="6"/>
+      <c r="Z623" s="6"/>
+    </row>
+    <row r="624" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="6"/>
       <c r="B624" s="6"/>
       <c r="C624" s="6"/>
@@ -45729,6 +46227,21 @@
       <c r="I624" s="9"/>
       <c r="J624" s="10"/>
       <c r="K624" s="10"/>
+      <c r="L624" s="6"/>
+      <c r="M624" s="6"/>
+      <c r="N624" s="6"/>
+      <c r="O624" s="6"/>
+      <c r="P624" s="6"/>
+      <c r="Q624" s="6"/>
+      <c r="R624" s="6"/>
+      <c r="S624" s="6"/>
+      <c r="T624" s="6"/>
+      <c r="U624" s="6"/>
+      <c r="V624" s="6"/>
+      <c r="W624" s="6"/>
+      <c r="X624" s="6"/>
+      <c r="Y624" s="6"/>
+      <c r="Z624" s="6"/>
     </row>
     <row r="625" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A625" s="6"/>
@@ -55922,6 +56435,32 @@
       <c r="J1408" s="10"/>
       <c r="K1408" s="10"/>
     </row>
+    <row r="1409" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1409" s="6"/>
+      <c r="B1409" s="6"/>
+      <c r="C1409" s="6"/>
+      <c r="D1409" s="6"/>
+      <c r="E1409" s="6"/>
+      <c r="F1409" s="7"/>
+      <c r="G1409" s="8"/>
+      <c r="H1409" s="6"/>
+      <c r="I1409" s="9"/>
+      <c r="J1409" s="10"/>
+      <c r="K1409" s="10"/>
+    </row>
+    <row r="1410" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1410" s="6"/>
+      <c r="B1410" s="6"/>
+      <c r="C1410" s="6"/>
+      <c r="D1410" s="6"/>
+      <c r="E1410" s="6"/>
+      <c r="F1410" s="7"/>
+      <c r="G1410" s="8"/>
+      <c r="H1410" s="6"/>
+      <c r="I1410" s="9"/>
+      <c r="J1410" s="10"/>
+      <c r="K1410" s="10"/>
+    </row>
   </sheetData>
   <autoFilter ref="A4:K553" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="2">
@@ -55932,42 +56471,42 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>'/Users/omarmaaouni/Documents/BERRY GOOD FARMS/LORAWAN/C:\Users\ACHRAF\OneDrive\Bureau\LA PRODUCTION\RAPPORT DE RODUCTION BERRY GOOD FARMS\[1ér cycle RAPPORT DE PRODUCTION BERRY GOOD FARMS.xlsx]Base'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>C5:E474 C554:E1408 H5:H474 H487:H511 C487:E511 H554:H1408</xm:sqref>
+          <xm:sqref>C5:E474 H5:H474 H487:H511 C487:E511 H577:H1410 C577:E1410</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
             <xm:f>'/Users/omarmaaouni/Documents/BERRY GOOD FARMS/LORAWAN/C:\Users\ACHRAF\OneDrive\Bureau\LA PRODUCTION\RAPPORT DE RODUCTION BERRY GOOD FARMS\[1ér cycle RAPPORT DE PRODUCTION BERRY GOOD FARMS.xlsx]Base'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>A487:A511 A554:A1408 A5:A474</xm:sqref>
+          <xm:sqref>A487:A511 A5:A474 A577:A1410</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000003000000}">
           <x14:formula1>
             <xm:f>'/Users/omarmaaouni/Documents/BERRY GOOD FARMS/LORAWAN/C:\Users\ACHRAF\OneDrive\Bureau\LA PRODUCTION\RAPPORT DE RODUCTION BERRY GOOD FARMS\[1ér cycle RAPPORT DE PRODUCTION BERRY GOOD FARMS.xlsx]Base'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>B487:B511 B554:B1408 B5:B474</xm:sqref>
+          <xm:sqref>B487:B511 B5:B474 B577:B1410</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-00002B000000}">
           <x14:formula1>
             <xm:f>'/Users/omarmaaouni/Documents/BERRY GOOD FARMS/LORAWAN/C:\Users\ACHRAF\OneDrive\Bureau\ACHRAF 2025 -2026\[1ér cycle RAPPORT DE PRODUCTION BERRY GOOD FARMS.xlsx]Base'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H512:H546 H548:H550 C512:E553 H475:H486 C475:E486</xm:sqref>
+          <xm:sqref>H512:H546 H548:H550 H475:H486 C475:E486 H554:H568 H572:H573 H575:H576 C512:E576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002D000000}">
           <x14:formula1>
             <xm:f>'/Users/omarmaaouni/Documents/BERRY GOOD FARMS/LORAWAN/C:\Users\ACHRAF\OneDrive\Bureau\ACHRAF 2025 -2026\[1ér cycle RAPPORT DE PRODUCTION BERRY GOOD FARMS.xlsx]Base'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>A475:A486 A512:A553</xm:sqref>
+          <xm:sqref>A475:A486 A512:A576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000030000000}">
           <x14:formula1>
             <xm:f>'/Users/omarmaaouni/Documents/BERRY GOOD FARMS/LORAWAN/C:\Users\ACHRAF\OneDrive\Bureau\ACHRAF 2025 -2026\[1ér cycle RAPPORT DE PRODUCTION BERRY GOOD FARMS.xlsx]Base'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>B475:B486 B512:B553</xm:sqref>
+          <xm:sqref>B475:B486 B512:B576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -55995,34 +56534,34 @@
   <sheetData>
     <row r="1" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="132" t="s">
+      <c r="A2" s="115" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="133"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="134"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="117"/>
     </row>
     <row r="3" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="135"/>
-      <c r="B3" s="136"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="137"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="120"/>
     </row>
     <row r="4" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:12" ht="35" thickBot="1" x14ac:dyDescent="0.25">
@@ -57100,24 +57639,24 @@
       <c r="L38" s="65"/>
     </row>
     <row r="39" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="138" t="s">
+      <c r="A39" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="139"/>
-      <c r="C39" s="139"/>
-      <c r="D39" s="139"/>
-      <c r="E39" s="139"/>
-      <c r="F39" s="139"/>
+      <c r="B39" s="122"/>
+      <c r="C39" s="122"/>
+      <c r="D39" s="122"/>
+      <c r="E39" s="122"/>
+      <c r="F39" s="122"/>
       <c r="G39" s="48">
         <f>SUM(G6:G13)</f>
         <v>132287.79999999999</v>
       </c>
-      <c r="H39" s="139" t="s">
+      <c r="H39" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="I39" s="139"/>
-      <c r="J39" s="139"/>
-      <c r="K39" s="139"/>
+      <c r="I39" s="122"/>
+      <c r="J39" s="122"/>
+      <c r="K39" s="122"/>
       <c r="L39" s="48" t="e">
         <f>SUM(L6:L23)</f>
         <v>#VALUE!</v>
@@ -57151,26 +57690,26 @@
   <sheetData>
     <row r="1" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="132" t="s">
+      <c r="B2" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="134"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="117"/>
     </row>
     <row r="3" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="135"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="137"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="120"/>
     </row>
     <row r="4" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:9" ht="35" thickBot="1" x14ac:dyDescent="0.25">
@@ -57240,15 +57779,15 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="138" t="s">
+      <c r="B8" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139"/>
-      <c r="F8" s="139"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="140"/>
+      <c r="C8" s="122"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="122"/>
+      <c r="F8" s="122"/>
+      <c r="G8" s="122"/>
+      <c r="H8" s="123"/>
       <c r="I8" s="21">
         <f>SUM(I6:I7)</f>
         <v>1852</v>
@@ -57279,20 +57818,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="142"/>
-      <c r="L1" s="143"/>
+      <c r="A1" s="124" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="126"/>
     </row>
     <row r="2" spans="1:27" ht="31" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -59260,27 +59799,27 @@
   <sheetData>
     <row r="4" spans="4:10" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="4:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D5" s="111" t="s">
+      <c r="D5" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="112"/>
-      <c r="F5" s="112"/>
-      <c r="G5" s="112"/>
-      <c r="H5" s="112"/>
-      <c r="I5" s="113"/>
+      <c r="E5" s="131"/>
+      <c r="F5" s="131"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="132"/>
     </row>
     <row r="6" spans="4:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D6" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="120" t="s">
+      <c r="E6" s="139" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="121"/>
-      <c r="G6" s="120" t="s">
+      <c r="F6" s="140"/>
+      <c r="G6" s="139" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="121"/>
+      <c r="H6" s="140"/>
       <c r="I6" s="96" t="s">
         <v>36</v>
       </c>
@@ -59289,16 +59828,16 @@
       <c r="D7" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="122">
+      <c r="E7" s="141">
         <f>SUMIFS('SITUATION LOCAL 2025-2026 '!$K$5:$K1301,'SITUATION LOCAL 2025-2026 '!$D$5:$D1301,D7)</f>
         <v>122038.93</v>
       </c>
-      <c r="F7" s="123"/>
-      <c r="G7" s="124">
+      <c r="F7" s="142"/>
+      <c r="G7" s="143">
         <f>SUMIFS(ENCAISEMENT!$L$3:$L98,ENCAISEMENT!$D$3:$D98,'RECAP DE SOLDE PAR CLIENT '!D7)</f>
         <v>139410</v>
       </c>
-      <c r="H7" s="123"/>
+      <c r="H7" s="142"/>
       <c r="I7" s="105">
         <f>E7-G7</f>
         <v>-17371.070000000007</v>
@@ -59311,16 +59850,16 @@
       <c r="D8" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="117">
+      <c r="E8" s="136">
         <f>SUMIFS('SITUATION LOCAL 2025-2026 '!$K$5:$K1999,'SITUATION LOCAL 2025-2026 '!$D$5:$D1999,D8)</f>
         <v>510016.4</v>
       </c>
-      <c r="F8" s="118"/>
-      <c r="G8" s="119">
+      <c r="F8" s="137"/>
+      <c r="G8" s="138">
         <f>SUMIFS(ENCAISEMENT!$L$3:$L100,ENCAISEMENT!$D$3:$D100,'RECAP DE SOLDE PAR CLIENT '!D8)</f>
         <v>552500</v>
       </c>
-      <c r="H8" s="118"/>
+      <c r="H8" s="137"/>
       <c r="I8" s="106">
         <f>E8-G8</f>
         <v>-42483.599999999977</v>
@@ -59333,16 +59872,16 @@
       <c r="D9" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="114" t="e">
+      <c r="E9" s="133" t="e">
         <f>'Situation de vente avocat '!L39</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F9" s="115"/>
-      <c r="G9" s="115">
+      <c r="F9" s="134"/>
+      <c r="G9" s="134">
         <f>SUMIFS(ENCAISEMENT!$L$3:$L102,ENCAISEMENT!$D$3:$D102,'RECAP DE SOLDE PAR CLIENT '!D9)</f>
         <v>300000</v>
       </c>
-      <c r="H9" s="116"/>
+      <c r="H9" s="135"/>
       <c r="I9" s="97" t="e">
         <f t="shared" ref="I9:I10" si="0">E9-G9</f>
         <v>#VALUE!</v>
@@ -59355,16 +59894,16 @@
       <c r="D10" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="114">
+      <c r="E10" s="133">
         <f>SUMIFS('Situation de vente Plastique '!I6:I7,'Situation de vente Plastique '!B6:B7,D10)</f>
         <v>1852</v>
       </c>
-      <c r="F10" s="115"/>
-      <c r="G10" s="115">
+      <c r="F10" s="134"/>
+      <c r="G10" s="134">
         <f>SUMIFS(ENCAISEMENT!L3:L40,ENCAISEMENT!D3:D40,D10)</f>
         <v>1850</v>
       </c>
-      <c r="H10" s="116"/>
+      <c r="H10" s="135"/>
       <c r="I10" s="97">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -59377,16 +59916,16 @@
       <c r="D11" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="114">
+      <c r="E11" s="133">
         <f>SUMIFS('SITUATION LOCAL 2025-2026 '!$K$5:$K1306,'SITUATION LOCAL 2025-2026 '!$D$5:$D1306,D11)</f>
         <v>13188</v>
       </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="115">
+      <c r="F11" s="135"/>
+      <c r="G11" s="134">
         <f>SUMIFS(ENCAISEMENT!L4:L41,ENCAISEMENT!D4:D41,D11)</f>
         <v>13188</v>
       </c>
-      <c r="H11" s="116"/>
+      <c r="H11" s="135"/>
       <c r="I11" s="97">
         <f t="shared" ref="I11" si="1">E11-G11</f>
         <v>0</v>
@@ -59399,16 +59938,16 @@
       <c r="D12" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="E12" s="108">
+      <c r="E12" s="127">
         <f>SUMIFS('SITUATION LOCAL 2025-2026 '!$K$5:$K2312,'SITUATION LOCAL 2025-2026 '!$D$5:$D2312,D12)</f>
         <v>58104</v>
       </c>
-      <c r="F12" s="109"/>
-      <c r="G12" s="110">
+      <c r="F12" s="128"/>
+      <c r="G12" s="129">
         <f>SUMIFS(ENCAISEMENT!L5:L42,ENCAISEMENT!D5:D42,D12)</f>
         <v>58104</v>
       </c>
-      <c r="H12" s="109"/>
+      <c r="H12" s="128"/>
       <c r="I12" s="107">
         <f t="shared" ref="I12" si="2">E12-G12</f>
         <v>0</v>
